--- a/finance/data/TO Score.xlsx
+++ b/finance/data/TO Score.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="입금현황" sheetId="1" state="visible" r:id="rId1"/>
@@ -824,14 +824,14 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -842,6 +842,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2038,7 +2058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W86"/>
+  <dimension ref="A1:W45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="9.375" bestFit="1" customWidth="1" style="97" min="2" max="2"/>
@@ -3623,20 +3643,20 @@
       <c r="G38" s="103" t="n"/>
       <c r="H38" s="103" t="n"/>
       <c r="I38" s="103" t="n"/>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="25" t="n"/>
-      <c r="L38" s="25" t="n"/>
-      <c r="M38" s="25" t="n"/>
-      <c r="N38" s="25" t="n"/>
-      <c r="O38" s="25" t="n"/>
-      <c r="P38" s="25" t="n"/>
-      <c r="Q38" s="25" t="n"/>
-      <c r="R38" s="25" t="n"/>
-      <c r="S38" s="25" t="n"/>
-      <c r="T38" s="25" t="n"/>
-      <c r="U38" s="25" t="n"/>
-      <c r="V38" s="25" t="n"/>
-      <c r="W38" s="25" t="n"/>
+      <c r="J38" s="103" t="n"/>
+      <c r="K38" s="103" t="n"/>
+      <c r="L38" s="103" t="n"/>
+      <c r="M38" s="103" t="n"/>
+      <c r="N38" s="103" t="n"/>
+      <c r="O38" s="103" t="n"/>
+      <c r="P38" s="103" t="n"/>
+      <c r="Q38" s="103" t="n"/>
+      <c r="R38" s="103" t="n"/>
+      <c r="S38" s="103" t="n"/>
+      <c r="T38" s="103" t="n"/>
+      <c r="U38" s="103" t="n"/>
+      <c r="V38" s="103" t="n"/>
+      <c r="W38" s="103" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -3663,20 +3683,20 @@
       <c r="G39" s="103" t="n"/>
       <c r="H39" s="103" t="n"/>
       <c r="I39" s="103" t="n"/>
-      <c r="J39" s="25" t="n"/>
-      <c r="K39" s="25" t="n"/>
-      <c r="L39" s="25" t="n"/>
-      <c r="M39" s="25" t="n"/>
-      <c r="N39" s="25" t="n"/>
-      <c r="O39" s="25" t="n"/>
-      <c r="P39" s="25" t="n"/>
-      <c r="Q39" s="25" t="n"/>
-      <c r="R39" s="25" t="n"/>
-      <c r="S39" s="25" t="n"/>
-      <c r="T39" s="25" t="n"/>
-      <c r="U39" s="25" t="n"/>
-      <c r="V39" s="25" t="n"/>
-      <c r="W39" s="25" t="n"/>
+      <c r="J39" s="103" t="n"/>
+      <c r="K39" s="103" t="n"/>
+      <c r="L39" s="103" t="n"/>
+      <c r="M39" s="103" t="n"/>
+      <c r="N39" s="103" t="n"/>
+      <c r="O39" s="103" t="n"/>
+      <c r="P39" s="103" t="n"/>
+      <c r="Q39" s="103" t="n"/>
+      <c r="R39" s="103" t="n"/>
+      <c r="S39" s="103" t="n"/>
+      <c r="T39" s="103" t="n"/>
+      <c r="U39" s="103" t="n"/>
+      <c r="V39" s="103" t="n"/>
+      <c r="W39" s="103" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -3953,50 +3973,14 @@
         <v/>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="73"/>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
-    <row r="77"/>
-    <row r="78"/>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
   </sheetData>
   <conditionalFormatting sqref="A2:A43">
-    <cfRule type="duplicateValues" priority="1" dxfId="1"/>
+    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:W43">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>20000</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4370,7 +4354,7 @@
         </is>
       </c>
       <c r="J16" s="118" t="n">
-        <v>1015127</v>
+        <v>1035127</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="97">
@@ -4428,7 +4412,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>

--- a/finance/data/TO Score.xlsx
+++ b/finance/data/TO Score.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="입금현황" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="회비입출내역" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="원장" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="증감분석" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="증감분석차트" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="참고" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="주요정보" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="참조" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="입금현황" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="회비입출내역" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="원장" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="증감분석" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="증감분석차트" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참고" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주요정보" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참조" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'회비입출내역'!$A$2:$J$15</definedName>
@@ -24,8 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0;[Red]\(#,##0\);&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -415,7 +416,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -711,12 +712,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -780,6 +779,7 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -818,20 +818,32 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="1"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -852,16 +864,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -939,14 +941,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="2000" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -970,8 +972,8 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -997,7 +999,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
@@ -1008,7 +1010,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1179,7 +1181,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
@@ -1190,7 +1192,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1361,7 +1363,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent4"/>
               </a:solidFill>
@@ -1372,7 +1374,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1552,8 +1554,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1565,9 +1567,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1582,7 +1584,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
@@ -1603,7 +1605,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1617,7 +1619,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1634,16 +1636,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1658,7 +1660,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
@@ -1674,16 +1676,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1698,7 +1700,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="ko-KR"/>
         </a:p>
@@ -1708,10 +1710,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1726,7 +1728,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -1746,9 +1748,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2282,7 +2284,9 @@
       <c r="E4" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F4" s="25" t="n"/>
+      <c r="F4" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G4" s="25" t="n"/>
       <c r="H4" s="25" t="n"/>
       <c r="I4" s="25" t="n"/>
@@ -2362,7 +2366,9 @@
       <c r="E6" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F6" s="25" t="n"/>
+      <c r="F6" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G6" s="25" t="n"/>
       <c r="H6" s="25" t="n"/>
       <c r="I6" s="25" t="n"/>
@@ -2402,7 +2408,9 @@
       <c r="E7" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F7" s="25" t="n"/>
+      <c r="F7" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G7" s="25" t="n"/>
       <c r="H7" s="25" t="n"/>
       <c r="I7" s="25" t="n"/>
@@ -2442,7 +2450,9 @@
       <c r="E8" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F8" s="25" t="n"/>
+      <c r="F8" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G8" s="25" t="n"/>
       <c r="H8" s="25" t="n"/>
       <c r="I8" s="25" t="n"/>
@@ -2562,7 +2572,9 @@
       <c r="E11" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F11" s="25" t="n"/>
+      <c r="F11" s="25" t="n">
+        <v>40000</v>
+      </c>
       <c r="G11" s="25" t="n"/>
       <c r="H11" s="25" t="n"/>
       <c r="I11" s="25" t="n"/>
@@ -2762,7 +2774,9 @@
       <c r="E16" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F16" s="25" t="n"/>
+      <c r="F16" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G16" s="25" t="n"/>
       <c r="H16" s="25" t="n"/>
       <c r="I16" s="25" t="n"/>
@@ -2802,7 +2816,9 @@
       <c r="E17" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F17" s="25" t="n"/>
+      <c r="F17" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G17" s="25" t="n"/>
       <c r="H17" s="25" t="n"/>
       <c r="I17" s="25" t="n"/>
@@ -2842,7 +2858,9 @@
       <c r="E18" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F18" s="25" t="n"/>
+      <c r="F18" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G18" s="25" t="n"/>
       <c r="H18" s="25" t="n"/>
       <c r="I18" s="25" t="n"/>
@@ -2922,7 +2940,9 @@
       <c r="E20" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F20" s="25" t="n"/>
+      <c r="F20" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G20" s="25" t="n"/>
       <c r="H20" s="25" t="n"/>
       <c r="I20" s="25" t="n"/>
@@ -3042,7 +3062,9 @@
       <c r="E23" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F23" s="103" t="n"/>
+      <c r="F23" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G23" s="103" t="n"/>
       <c r="H23" s="103" t="n"/>
       <c r="I23" s="103" t="n"/>
@@ -3080,7 +3102,7 @@
         <v>20000</v>
       </c>
       <c r="E24" s="103" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F24" s="103" t="n"/>
       <c r="G24" s="103" t="n"/>
@@ -3122,7 +3144,9 @@
       <c r="E25" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F25" s="103" t="n"/>
+      <c r="F25" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G25" s="103" t="n"/>
       <c r="H25" s="103" t="n"/>
       <c r="I25" s="103" t="n"/>
@@ -3202,7 +3226,9 @@
       <c r="E27" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F27" s="103" t="n"/>
+      <c r="F27" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G27" s="103" t="n"/>
       <c r="H27" s="103" t="n"/>
       <c r="I27" s="103" t="n"/>
@@ -3282,7 +3308,9 @@
       <c r="E29" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F29" s="103" t="n"/>
+      <c r="F29" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G29" s="103" t="n"/>
       <c r="H29" s="103" t="n"/>
       <c r="I29" s="103" t="n"/>
@@ -3322,7 +3350,9 @@
       <c r="E30" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F30" s="103" t="n"/>
+      <c r="F30" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G30" s="103" t="n"/>
       <c r="H30" s="103" t="n"/>
       <c r="I30" s="103" t="n"/>
@@ -3400,9 +3430,11 @@
         <v>20000</v>
       </c>
       <c r="E32" s="103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="103" t="n"/>
+        <v>20000</v>
+      </c>
+      <c r="F32" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G32" s="103" t="n"/>
       <c r="H32" s="103" t="n"/>
       <c r="I32" s="103" t="n"/>
@@ -3427,7 +3459,7 @@
           <t>김지수</t>
         </is>
       </c>
-      <c r="B33" s="100" t="inlineStr">
+      <c r="B33" s="99" t="inlineStr">
         <is>
           <t>탈퇴</t>
         </is>
@@ -3480,7 +3512,9 @@
       <c r="E34" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F34" s="103" t="n"/>
+      <c r="F34" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G34" s="103" t="n"/>
       <c r="H34" s="103" t="n"/>
       <c r="I34" s="103" t="n"/>
@@ -3600,7 +3634,9 @@
       <c r="E37" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F37" s="103" t="n"/>
+      <c r="F37" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G37" s="103" t="n"/>
       <c r="H37" s="103" t="n"/>
       <c r="I37" s="103" t="n"/>
@@ -3679,7 +3715,9 @@
       <c r="E39" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F39" s="103" t="n"/>
+      <c r="F39" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G39" s="103" t="n"/>
       <c r="H39" s="103" t="n"/>
       <c r="I39" s="103" t="n"/>
@@ -3719,7 +3757,9 @@
       <c r="E40" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F40" s="103" t="n"/>
+      <c r="F40" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G40" s="103" t="n"/>
       <c r="H40" s="103" t="n"/>
       <c r="I40" s="103" t="n"/>
@@ -3757,7 +3797,7 @@
         <v>20000</v>
       </c>
       <c r="E41" s="103" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F41" s="103" t="n"/>
       <c r="G41" s="103" t="n"/>
@@ -3799,7 +3839,9 @@
       <c r="E42" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F42" s="103" t="n"/>
+      <c r="F42" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G42" s="103" t="n"/>
       <c r="H42" s="103" t="n"/>
       <c r="I42" s="103" t="n"/>
@@ -3837,7 +3879,9 @@
       <c r="E43" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F43" s="103" t="n"/>
+      <c r="F43" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G43" s="103" t="n"/>
       <c r="H43" s="103" t="n"/>
       <c r="I43" s="103" t="n"/>
@@ -3856,30 +3900,43 @@
       <c r="V43" s="25" t="n"/>
       <c r="W43" s="25" t="n"/>
     </row>
-    <row r="44" ht="5.25" customHeight="1" s="97">
-      <c r="A44" s="98" t="n"/>
-      <c r="B44" s="98" t="n"/>
-      <c r="C44" s="98" t="n"/>
+    <row r="44" ht="34.5" customHeight="1" s="97">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>박정수</t>
+        </is>
+      </c>
+      <c r="B44" s="101" t="inlineStr">
+        <is>
+          <t>유지</t>
+        </is>
+      </c>
+      <c r="C44" s="102">
+        <f>SUM(D44:CD44)</f>
+        <v/>
+      </c>
       <c r="D44" s="98" t="n"/>
-      <c r="E44" s="98" t="n"/>
-      <c r="F44" s="98" t="n"/>
-      <c r="G44" s="98" t="n"/>
-      <c r="H44" s="98" t="n"/>
-      <c r="I44" s="98" t="n"/>
-      <c r="J44" s="98" t="n"/>
-      <c r="K44" s="98" t="n"/>
-      <c r="L44" s="98" t="n"/>
-      <c r="M44" s="98" t="n"/>
-      <c r="N44" s="98" t="n"/>
-      <c r="O44" s="99" t="n"/>
-      <c r="P44" s="99" t="n"/>
-      <c r="Q44" s="99" t="n"/>
-      <c r="R44" s="99" t="n"/>
-      <c r="S44" s="99" t="n"/>
-      <c r="T44" s="99" t="n"/>
-      <c r="U44" s="99" t="n"/>
-      <c r="V44" s="99" t="n"/>
-      <c r="W44" s="99" t="n"/>
+      <c r="E44" s="103" t="n"/>
+      <c r="F44" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G44" s="103" t="n"/>
+      <c r="H44" s="103" t="n"/>
+      <c r="I44" s="103" t="n"/>
+      <c r="J44" s="25" t="n"/>
+      <c r="K44" s="25" t="n"/>
+      <c r="L44" s="25" t="n"/>
+      <c r="M44" s="25" t="n"/>
+      <c r="N44" s="25" t="n"/>
+      <c r="O44" s="25" t="n"/>
+      <c r="P44" s="25" t="n"/>
+      <c r="Q44" s="25" t="n"/>
+      <c r="R44" s="25" t="n"/>
+      <c r="S44" s="25" t="n"/>
+      <c r="T44" s="25" t="n"/>
+      <c r="U44" s="25" t="n"/>
+      <c r="V44" s="25" t="n"/>
+      <c r="W44" s="25" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -3975,10 +4032,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A43">
-    <cfRule type="duplicateValues" priority="2" dxfId="0"/>
+    <cfRule type="duplicateValues" priority="2" dxfId="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:W43">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="1">
       <formula>20000</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4350,11 +4407,11 @@
       <c r="H16" s="17" t="n"/>
       <c r="I16" s="117" t="inlineStr">
         <is>
-          <t>5월 5일 잔액</t>
+          <t>7월 1일 잔액</t>
         </is>
       </c>
       <c r="J16" s="118" t="n">
-        <v>1035127</v>
+        <v>957190</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="97">
@@ -4412,7 +4469,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J17">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4427,12 +4484,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="13.25" customWidth="1" style="97" min="1" max="1"/>
     <col width="8.75" customWidth="1" style="97" min="2" max="2"/>
-    <col width="13.25" customWidth="1" style="97" min="3" max="8"/>
+    <col width="15.25" customWidth="1" style="97" min="3" max="3"/>
+    <col width="13.25" customWidth="1" style="97" min="4" max="8"/>
     <col width="25.875" customWidth="1" style="97" min="9" max="9"/>
     <col width="9.375" bestFit="1" customWidth="1" style="97" min="10" max="10"/>
     <col width="11" customWidth="1" style="97" min="11" max="11"/>
@@ -4688,7 +4746,7 @@
         <v/>
       </c>
       <c r="C7" s="13" t="n">
-        <v>46159</v>
+        <v>46174</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
@@ -4710,190 +4768,371 @@
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>황인호, 현수막 제작 등</t>
+          <t>황인호, 현수막 제작 등 (은행확인 6/1)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9">
+      <c r="A8" s="4">
         <f>RIGHT(YEAR(C8),2)&amp;"년 "&amp;MONTH(C8)&amp;"월"</f>
         <v/>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="4">
         <f>VLOOKUP(WEEKDAY(C8,2),참조!$A$1:$B$10,2,)</f>
         <v/>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="136" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D8" s="136" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="E8" s="136" t="inlineStr">
+        <is>
+          <t>경품비</t>
+        </is>
+      </c>
+      <c r="F8" s="137" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G8" s="137" t="n"/>
+      <c r="H8" s="138">
+        <f>G8-F8</f>
+        <v/>
+      </c>
+      <c r="I8" s="139" t="inlineStr">
+        <is>
+          <t>대회 당일 카카오페이 정산(6건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4">
+        <f>RIGHT(YEAR(C9),2)&amp;"년 "&amp;MONTH(C9)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B9" s="4">
+        <f>VLOOKUP(WEEKDAY(C9,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C9" s="136" t="n">
+        <v>46185</v>
+      </c>
+      <c r="D9" s="136" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="E9" s="136" t="inlineStr">
+        <is>
+          <t>경품비</t>
+        </is>
+      </c>
+      <c r="F9" s="137" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G9" s="137" t="n"/>
+      <c r="H9" s="138">
+        <f>G9-F9</f>
+        <v/>
+      </c>
+      <c r="I9" s="139" t="inlineStr">
+        <is>
+          <t>옥지엽 이체</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4">
+        <f>RIGHT(YEAR(C10),2)&amp;"년 "&amp;MONTH(C10)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B10" s="4">
+        <f>VLOOKUP(WEEKDAY(C10,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C10" s="136" t="n">
+        <v>46187</v>
+      </c>
+      <c r="D10" s="136" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="E10" s="136" t="inlineStr">
+        <is>
+          <t>모임비</t>
+        </is>
+      </c>
+      <c r="F10" s="137" t="n">
+        <v>328000</v>
+      </c>
+      <c r="G10" s="137" t="n"/>
+      <c r="H10" s="138">
+        <f>G10-F10</f>
+        <v/>
+      </c>
+      <c r="I10" s="139" t="inlineStr">
+        <is>
+          <t>황인호, 술값</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4">
+        <f>RIGHT(YEAR(C11),2)&amp;"년 "&amp;MONTH(C11)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B11" s="4">
+        <f>VLOOKUP(WEEKDAY(C11,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C11" s="136" t="n">
+        <v>46200</v>
+      </c>
+      <c r="D11" s="136" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="E11" s="136" t="inlineStr">
+        <is>
+          <t>이자</t>
+        </is>
+      </c>
+      <c r="F11" s="137" t="n"/>
+      <c r="G11" s="137" t="n">
+        <v>63</v>
+      </c>
+      <c r="H11" s="138">
+        <f>G11-F11</f>
+        <v/>
+      </c>
+      <c r="I11" s="139" t="inlineStr">
+        <is>
+          <t>월간이자</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4">
+        <f>RIGHT(YEAR(C12),2)&amp;"년 "&amp;MONTH(C12)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B12" s="4">
+        <f>VLOOKUP(WEEKDAY(C12,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C12" s="136" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D12" s="136" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="E12" s="136" t="inlineStr">
+        <is>
+          <t>회비</t>
+        </is>
+      </c>
+      <c r="F12" s="137" t="n"/>
+      <c r="G12" s="137">
+        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="138">
+        <f>G12-F12</f>
+        <v/>
+      </c>
+      <c r="I12" s="139" t="inlineStr">
+        <is>
+          <t>월간회비납부</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9">
+        <f>RIGHT(YEAR(C13),2)&amp;"년 "&amp;MONTH(C13)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B13" s="9">
+        <f>VLOOKUP(WEEKDAY(C13,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C13" s="13" t="n">
         <v>46235</v>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>입금</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>회비</t>
         </is>
       </c>
-      <c r="F8" s="120" t="n"/>
-      <c r="G8" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="121">
-        <f>G8-F8</f>
-        <v/>
-      </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="F13" s="120" t="n"/>
+      <c r="G13" s="120">
+        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="121">
+        <f>G13-F13</f>
+        <v/>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>월간회비납부</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9">
-        <f>RIGHT(YEAR(C9),2)&amp;"년 "&amp;MONTH(C9)&amp;"월"</f>
-        <v/>
-      </c>
-      <c r="B9" s="9">
-        <f>VLOOKUP(WEEKDAY(C9,2),참조!$A$1:$B$10,2,)</f>
-        <v/>
-      </c>
-      <c r="C9" s="13" t="n">
+    <row r="14">
+      <c r="A14" s="9">
+        <f>RIGHT(YEAR(C14),2)&amp;"년 "&amp;MONTH(C14)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B14" s="9">
+        <f>VLOOKUP(WEEKDAY(C14,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C14" s="13" t="n">
         <v>46266</v>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>입금</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>회비</t>
         </is>
       </c>
-      <c r="F9" s="120" t="n"/>
-      <c r="G9" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="121">
-        <f>G9-F9</f>
-        <v/>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="F14" s="120" t="n"/>
+      <c r="G14" s="120">
+        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="121">
+        <f>G14-F14</f>
+        <v/>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>월간회비납부</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9">
-        <f>RIGHT(YEAR(C10),2)&amp;"년 "&amp;MONTH(C10)&amp;"월"</f>
-        <v/>
-      </c>
-      <c r="B10" s="9">
-        <f>VLOOKUP(WEEKDAY(C10,2),참조!$A$1:$B$10,2,)</f>
-        <v/>
-      </c>
-      <c r="C10" s="13" t="n">
+    <row r="15">
+      <c r="A15" s="9">
+        <f>RIGHT(YEAR(C15),2)&amp;"년 "&amp;MONTH(C15)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B15" s="9">
+        <f>VLOOKUP(WEEKDAY(C15,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C15" s="13" t="n">
         <v>46296</v>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>입금</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>회비</t>
         </is>
       </c>
-      <c r="F10" s="120" t="n"/>
-      <c r="G10" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="121">
-        <f>G10-F10</f>
-        <v/>
-      </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="F15" s="120" t="n"/>
+      <c r="G15" s="120">
+        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="121">
+        <f>G15-F15</f>
+        <v/>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>월간회비납부</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9">
-        <f>RIGHT(YEAR(C11),2)&amp;"년 "&amp;MONTH(C11)&amp;"월"</f>
-        <v/>
-      </c>
-      <c r="B11" s="9">
-        <f>VLOOKUP(WEEKDAY(C11,2),참조!$A$1:$B$10,2,)</f>
-        <v/>
-      </c>
-      <c r="C11" s="13" t="n">
+    <row r="16">
+      <c r="A16" s="9">
+        <f>RIGHT(YEAR(C16),2)&amp;"년 "&amp;MONTH(C16)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B16" s="9">
+        <f>VLOOKUP(WEEKDAY(C16,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C16" s="13" t="n">
         <v>46327</v>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>입금</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>회비</t>
         </is>
       </c>
-      <c r="F11" s="120" t="n"/>
-      <c r="G11" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="121">
-        <f>G11-F11</f>
-        <v/>
-      </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="F16" s="120" t="n"/>
+      <c r="G16" s="120">
+        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="121">
+        <f>G16-F16</f>
+        <v/>
+      </c>
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>월간회비납부</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9">
-        <f>RIGHT(YEAR(C12),2)&amp;"년 "&amp;MONTH(C12)&amp;"월"</f>
-        <v/>
-      </c>
-      <c r="B12" s="9">
-        <f>VLOOKUP(WEEKDAY(C12,2),참조!$A$1:$B$10,2,)</f>
-        <v/>
-      </c>
-      <c r="C12" s="13" t="n">
+    <row r="17">
+      <c r="A17" s="9">
+        <f>RIGHT(YEAR(C17),2)&amp;"년 "&amp;MONTH(C17)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B17" s="9">
+        <f>VLOOKUP(WEEKDAY(C17,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C17" s="13" t="n">
         <v>46357</v>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>입금</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>회비</t>
         </is>
       </c>
-      <c r="F12" s="120" t="n"/>
-      <c r="G12" s="120">
-        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="121">
-        <f>G12-F12</f>
-        <v/>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="F17" s="120" t="n"/>
+      <c r="G17" s="120">
+        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="121">
+        <f>G17-F17</f>
+        <v/>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>월간회비납부</t>
         </is>
@@ -5010,39 +5249,39 @@
         </is>
       </c>
       <c r="C4" s="55" t="n"/>
-      <c r="D4" s="122">
+      <c r="D4" s="123">
         <f>AVERAGEIFS(D10:D2203,D10:D2203,"&gt;0")</f>
         <v/>
       </c>
-      <c r="E4" s="122">
+      <c r="E4" s="123">
         <f>AVERAGEIFS(E10:E2203,E10:E2203,"&gt;0")</f>
         <v/>
       </c>
-      <c r="F4" s="122">
+      <c r="F4" s="123">
         <f>AVERAGEIFS(F10:F2203,F10:F2203,"&gt;0")</f>
         <v/>
       </c>
-      <c r="G4" s="122">
+      <c r="G4" s="123">
         <f>AVERAGEIFS(G10:G2203,G10:G2203,"&gt;0")</f>
         <v/>
       </c>
-      <c r="H4" s="122">
+      <c r="H4" s="123">
         <f>AVERAGEIFS(H10:H2203,H10:H2203,"&lt;0")</f>
         <v/>
       </c>
-      <c r="I4" s="123">
+      <c r="I4" s="124">
         <f>AVERAGEIFS(I10:I2203,I10:I2203,"&lt;0")</f>
         <v/>
       </c>
-      <c r="J4" s="123">
+      <c r="J4" s="124">
         <f>AVERAGEIFS(J10:J2203,J10:J2203,"&lt;0")</f>
         <v/>
       </c>
-      <c r="K4" s="123">
+      <c r="K4" s="124">
         <f>AVERAGEIFS(K10:K2203,K10:K2203,"&lt;0")</f>
         <v/>
       </c>
-      <c r="L4" s="123">
+      <c r="L4" s="124">
         <f>AVERAGEIFS(L10:L2203,L10:L2203,"&lt;0")</f>
         <v/>
       </c>
@@ -5057,39 +5296,39 @@
         </is>
       </c>
       <c r="C5" s="55" t="n"/>
-      <c r="D5" s="122">
+      <c r="D5" s="123">
         <f>AVERAGEIFS(D8:D2201,$C$10:$C$2203,"&lt;=3")</f>
         <v/>
       </c>
-      <c r="E5" s="122">
+      <c r="E5" s="123">
         <f>AVERAGEIFS(E8:E2201,$C$10:$C$2203,"&lt;=3")</f>
         <v/>
       </c>
-      <c r="F5" s="122">
+      <c r="F5" s="123">
         <f>AVERAGEIFS(F8:F2201,$C$10:$C$2203,"&lt;=3")</f>
         <v/>
       </c>
-      <c r="G5" s="124">
+      <c r="G5" s="125">
         <f>AVERAGEIFS(G8:G2201,$C$10:$C$2203,"&lt;=3")</f>
         <v/>
       </c>
-      <c r="H5" s="122">
+      <c r="H5" s="123">
         <f>AVERAGEIFS(H$10:H$2203,$C$10:$C$2203,"&lt;=3")</f>
         <v/>
       </c>
-      <c r="I5" s="122">
+      <c r="I5" s="123">
         <f>AVERAGEIFS(I$10:I$2203,$C$10:$C$2203,"&lt;=3")</f>
         <v/>
       </c>
-      <c r="J5" s="122">
+      <c r="J5" s="123">
         <f>AVERAGEIFS(J$10:J$2203,$C$10:$C$2203,"&lt;=3")</f>
         <v/>
       </c>
-      <c r="K5" s="122">
+      <c r="K5" s="123">
         <f>AVERAGEIFS(K$10:K$2203,$C$10:$C$2203,"&lt;=3")</f>
         <v/>
       </c>
-      <c r="L5" s="125">
+      <c r="L5" s="126">
         <f>AVERAGEIFS(L$10:L$2203,$C$10:$C$2203,"&lt;=3")</f>
         <v/>
       </c>
@@ -5104,39 +5343,39 @@
         </is>
       </c>
       <c r="C6" s="55" t="n"/>
-      <c r="D6" s="122">
+      <c r="D6" s="123">
         <f>AVERAGEIFS(D9:D2202,$C$10:$C$2203,"&lt;=6")</f>
         <v/>
       </c>
-      <c r="E6" s="122">
+      <c r="E6" s="123">
         <f>AVERAGEIFS(E9:E2202,$C$10:$C$2203,"&lt;=6")</f>
         <v/>
       </c>
-      <c r="F6" s="122">
+      <c r="F6" s="123">
         <f>AVERAGEIFS(F9:F2202,$C$10:$C$2203,"&lt;=6")</f>
         <v/>
       </c>
-      <c r="G6" s="124">
+      <c r="G6" s="125">
         <f>AVERAGEIFS(G9:G2202,$C$10:$C$2203,"&lt;=6")</f>
         <v/>
       </c>
-      <c r="H6" s="122">
+      <c r="H6" s="123">
         <f>AVERAGEIFS(H$10:H$2203,$C$10:$C$2203,"&lt;=6")</f>
         <v/>
       </c>
-      <c r="I6" s="122">
+      <c r="I6" s="123">
         <f>AVERAGEIFS(I$10:I$2203,$C$10:$C$2203,"&lt;=6")</f>
         <v/>
       </c>
-      <c r="J6" s="122">
+      <c r="J6" s="123">
         <f>AVERAGEIFS(J$10:J$2203,$C$10:$C$2203,"&lt;=6")</f>
         <v/>
       </c>
-      <c r="K6" s="122">
+      <c r="K6" s="123">
         <f>AVERAGEIFS(K$10:K$2203,$C$10:$C$2203,"&lt;=6")</f>
         <v/>
       </c>
-      <c r="L6" s="125">
+      <c r="L6" s="126">
         <f>AVERAGEIFS(L$10:L$2203,$C$10:$C$2203,"&lt;=6")</f>
         <v/>
       </c>
@@ -5151,39 +5390,39 @@
         </is>
       </c>
       <c r="C7" s="55" t="n"/>
-      <c r="D7" s="122">
+      <c r="D7" s="123">
         <f>AVERAGEIFS(D10:D2203,$C$10:$C$2203,"&lt;=12")</f>
         <v/>
       </c>
-      <c r="E7" s="122">
+      <c r="E7" s="123">
         <f>AVERAGEIFS(E10:E2203,$C$10:$C$2203,"&lt;=12")</f>
         <v/>
       </c>
-      <c r="F7" s="122">
+      <c r="F7" s="123">
         <f>AVERAGEIFS(F10:F2203,$C$10:$C$2203,"&lt;=12")</f>
         <v/>
       </c>
-      <c r="G7" s="124">
+      <c r="G7" s="125">
         <f>AVERAGEIFS(G10:G2203,$C$10:$C$2203,"&lt;=12")</f>
         <v/>
       </c>
-      <c r="H7" s="122">
+      <c r="H7" s="123">
         <f>AVERAGEIFS(H$10:H$2203,$C$10:$C$2203,"&lt;=12")</f>
         <v/>
       </c>
-      <c r="I7" s="122">
+      <c r="I7" s="123">
         <f>AVERAGEIFS(I$10:I$2203,$C$10:$C$2203,"&lt;=12")</f>
         <v/>
       </c>
-      <c r="J7" s="122">
+      <c r="J7" s="123">
         <f>AVERAGEIFS(J$10:J$2203,$C$10:$C$2203,"&lt;=12")</f>
         <v/>
       </c>
-      <c r="K7" s="122">
+      <c r="K7" s="123">
         <f>AVERAGEIFS(K$10:K$2203,$C$10:$C$2203,"&lt;=12")</f>
         <v/>
       </c>
-      <c r="L7" s="125">
+      <c r="L7" s="126">
         <f>AVERAGEIFS(L$10:L$2203,$C$10:$C$2203,"&lt;=12")</f>
         <v/>
       </c>
@@ -5353,47 +5592,47 @@
         <f>IF($B11=참고!$D$5,1,C12+1)</f>
         <v/>
       </c>
-      <c r="D11" s="122">
+      <c r="D11" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B11,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E11" s="122">
+      <c r="E11" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B11,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F11" s="122">
+      <c r="F11" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B11,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G11" s="122">
+      <c r="G11" s="123">
         <f>SUM(D11:F11)</f>
         <v/>
       </c>
-      <c r="H11" s="122">
+      <c r="H11" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B11,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I11" s="122">
+      <c r="I11" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B11,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B11,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K11" s="122">
+      <c r="K11" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B11,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="123">
         <f>SUM(H11:K11)</f>
         <v/>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="123">
         <f>G11+L11</f>
         <v/>
       </c>
-      <c r="N11" s="122">
+      <c r="N11" s="123">
         <f>SUM($M$11:M11)</f>
         <v/>
       </c>
@@ -5401,15 +5640,15 @@
         <f>B11</f>
         <v/>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="123">
         <f>G11</f>
         <v/>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="127">
         <f>-L11</f>
         <v/>
       </c>
-      <c r="S11" s="122">
+      <c r="S11" s="123">
         <f>N11</f>
         <v/>
       </c>
@@ -5424,47 +5663,47 @@
         <f>IF($B12=참고!$D$5,1,C13+1)</f>
         <v/>
       </c>
-      <c r="D12" s="122">
+      <c r="D12" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B12,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E12" s="122">
+      <c r="E12" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B12,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F12" s="122">
+      <c r="F12" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B12,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G12" s="122">
+      <c r="G12" s="123">
         <f>SUM(D12:F12)</f>
         <v/>
       </c>
-      <c r="H12" s="122">
+      <c r="H12" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B12,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I12" s="122">
+      <c r="I12" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B12,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J12" s="122">
+      <c r="J12" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B12,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K12" s="122">
+      <c r="K12" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B12,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L12" s="122">
+      <c r="L12" s="123">
         <f>SUM(H12:K12)</f>
         <v/>
       </c>
-      <c r="M12" s="122">
+      <c r="M12" s="123">
         <f>G12+L12</f>
         <v/>
       </c>
-      <c r="N12" s="122">
+      <c r="N12" s="123">
         <f>SUM($M$11:M12)</f>
         <v/>
       </c>
@@ -5472,15 +5711,15 @@
         <f>B12</f>
         <v/>
       </c>
-      <c r="Q12" s="122">
+      <c r="Q12" s="123">
         <f>G12</f>
         <v/>
       </c>
-      <c r="R12" s="126">
+      <c r="R12" s="127">
         <f>-L12</f>
         <v/>
       </c>
-      <c r="S12" s="122">
+      <c r="S12" s="123">
         <f>N12</f>
         <v/>
       </c>
@@ -5495,47 +5734,47 @@
         <f>IF($B13=참고!$D$5,1,C14+1)</f>
         <v/>
       </c>
-      <c r="D13" s="122">
+      <c r="D13" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B13,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E13" s="122">
+      <c r="E13" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B13,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F13" s="122">
+      <c r="F13" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B13,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G13" s="122">
+      <c r="G13" s="123">
         <f>SUM(D13:F13)</f>
         <v/>
       </c>
-      <c r="H13" s="122">
+      <c r="H13" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B13,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I13" s="122">
+      <c r="I13" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B13,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J13" s="122">
+      <c r="J13" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B13,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K13" s="122">
+      <c r="K13" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B13,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L13" s="122">
+      <c r="L13" s="123">
         <f>SUM(H13:K13)</f>
         <v/>
       </c>
-      <c r="M13" s="122">
+      <c r="M13" s="123">
         <f>G13+L13</f>
         <v/>
       </c>
-      <c r="N13" s="122">
+      <c r="N13" s="123">
         <f>SUM($M$11:M13)</f>
         <v/>
       </c>
@@ -5543,15 +5782,15 @@
         <f>B13</f>
         <v/>
       </c>
-      <c r="Q13" s="122">
+      <c r="Q13" s="123">
         <f>G13</f>
         <v/>
       </c>
-      <c r="R13" s="126">
+      <c r="R13" s="127">
         <f>-L13</f>
         <v/>
       </c>
-      <c r="S13" s="122">
+      <c r="S13" s="123">
         <f>N13</f>
         <v/>
       </c>
@@ -5566,47 +5805,47 @@
         <f>IF($B14=참고!$D$5,1,C15+1)</f>
         <v/>
       </c>
-      <c r="D14" s="122">
+      <c r="D14" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B14,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E14" s="122">
+      <c r="E14" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B14,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F14" s="122">
+      <c r="F14" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B14,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G14" s="122">
+      <c r="G14" s="123">
         <f>SUM(D14:F14)</f>
         <v/>
       </c>
-      <c r="H14" s="122">
+      <c r="H14" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B14,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I14" s="122">
+      <c r="I14" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B14,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J14" s="122">
+      <c r="J14" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B14,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K14" s="122">
+      <c r="K14" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B14,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L14" s="122">
+      <c r="L14" s="123">
         <f>SUM(H14:K14)</f>
         <v/>
       </c>
-      <c r="M14" s="122">
+      <c r="M14" s="123">
         <f>G14+L14</f>
         <v/>
       </c>
-      <c r="N14" s="122">
+      <c r="N14" s="123">
         <f>SUM($M$11:M14)</f>
         <v/>
       </c>
@@ -5614,15 +5853,15 @@
         <f>B14</f>
         <v/>
       </c>
-      <c r="Q14" s="122">
+      <c r="Q14" s="123">
         <f>G14</f>
         <v/>
       </c>
-      <c r="R14" s="126">
+      <c r="R14" s="127">
         <f>-L14</f>
         <v/>
       </c>
-      <c r="S14" s="122">
+      <c r="S14" s="123">
         <f>N14</f>
         <v/>
       </c>
@@ -5637,47 +5876,47 @@
         <f>IF($B15=참고!$D$5,1,C16+1)</f>
         <v/>
       </c>
-      <c r="D15" s="122">
+      <c r="D15" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B15,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E15" s="122">
+      <c r="E15" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B15,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F15" s="122">
+      <c r="F15" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B15,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G15" s="122">
+      <c r="G15" s="123">
         <f>SUM(D15:F15)</f>
         <v/>
       </c>
-      <c r="H15" s="122">
+      <c r="H15" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B15,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I15" s="122">
+      <c r="I15" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B15,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J15" s="122">
+      <c r="J15" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B15,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K15" s="122">
+      <c r="K15" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B15,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L15" s="122">
+      <c r="L15" s="123">
         <f>SUM(H15:K15)</f>
         <v/>
       </c>
-      <c r="M15" s="122">
+      <c r="M15" s="123">
         <f>G15+L15</f>
         <v/>
       </c>
-      <c r="N15" s="122">
+      <c r="N15" s="123">
         <f>SUM($M$11:M15)</f>
         <v/>
       </c>
@@ -5685,15 +5924,15 @@
         <f>B15</f>
         <v/>
       </c>
-      <c r="Q15" s="122">
+      <c r="Q15" s="123">
         <f>G15</f>
         <v/>
       </c>
-      <c r="R15" s="126">
+      <c r="R15" s="127">
         <f>-L15</f>
         <v/>
       </c>
-      <c r="S15" s="122">
+      <c r="S15" s="123">
         <f>N15</f>
         <v/>
       </c>
@@ -5708,47 +5947,47 @@
         <f>IF($B16=참고!$D$5,1,C17+1)</f>
         <v/>
       </c>
-      <c r="D16" s="122">
+      <c r="D16" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B16,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E16" s="122">
+      <c r="E16" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B16,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F16" s="122">
+      <c r="F16" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B16,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G16" s="122">
+      <c r="G16" s="123">
         <f>SUM(D16:F16)</f>
         <v/>
       </c>
-      <c r="H16" s="122">
+      <c r="H16" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B16,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I16" s="122">
+      <c r="I16" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B16,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J16" s="122">
+      <c r="J16" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B16,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K16" s="122">
+      <c r="K16" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B16,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L16" s="122">
+      <c r="L16" s="123">
         <f>SUM(H16:K16)</f>
         <v/>
       </c>
-      <c r="M16" s="122">
+      <c r="M16" s="123">
         <f>G16+L16</f>
         <v/>
       </c>
-      <c r="N16" s="122">
+      <c r="N16" s="123">
         <f>SUM($M$11:M16)</f>
         <v/>
       </c>
@@ -5756,15 +5995,15 @@
         <f>B16</f>
         <v/>
       </c>
-      <c r="Q16" s="122">
+      <c r="Q16" s="123">
         <f>G16</f>
         <v/>
       </c>
-      <c r="R16" s="126">
+      <c r="R16" s="127">
         <f>-L16</f>
         <v/>
       </c>
-      <c r="S16" s="122">
+      <c r="S16" s="123">
         <f>N16</f>
         <v/>
       </c>
@@ -5779,47 +6018,47 @@
         <f>IF($B17=참고!$D$5,1,C18+1)</f>
         <v/>
       </c>
-      <c r="D17" s="122">
+      <c r="D17" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B17,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E17" s="122">
+      <c r="E17" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B17,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F17" s="122">
+      <c r="F17" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B17,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G17" s="122">
+      <c r="G17" s="123">
         <f>SUM(D17:F17)</f>
         <v/>
       </c>
-      <c r="H17" s="122">
+      <c r="H17" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B17,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I17" s="122">
+      <c r="I17" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B17,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J17" s="122">
+      <c r="J17" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B17,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K17" s="122">
+      <c r="K17" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B17,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L17" s="122">
+      <c r="L17" s="123">
         <f>SUM(H17:K17)</f>
         <v/>
       </c>
-      <c r="M17" s="122">
+      <c r="M17" s="123">
         <f>G17+L17</f>
         <v/>
       </c>
-      <c r="N17" s="122">
+      <c r="N17" s="123">
         <f>SUM($M$11:M17)</f>
         <v/>
       </c>
@@ -5827,15 +6066,15 @@
         <f>B17</f>
         <v/>
       </c>
-      <c r="Q17" s="122">
+      <c r="Q17" s="123">
         <f>G17</f>
         <v/>
       </c>
-      <c r="R17" s="126">
+      <c r="R17" s="127">
         <f>-L17</f>
         <v/>
       </c>
-      <c r="S17" s="122">
+      <c r="S17" s="123">
         <f>N17</f>
         <v/>
       </c>
@@ -5850,47 +6089,47 @@
         <f>IF($B18=참고!$D$5,1,C19+1)</f>
         <v/>
       </c>
-      <c r="D18" s="122">
+      <c r="D18" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B18,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E18" s="122">
+      <c r="E18" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B18,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F18" s="122">
+      <c r="F18" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B18,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G18" s="122">
+      <c r="G18" s="123">
         <f>SUM(D18:F18)</f>
         <v/>
       </c>
-      <c r="H18" s="122">
+      <c r="H18" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B18,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I18" s="122">
+      <c r="I18" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B18,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J18" s="122">
+      <c r="J18" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B18,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K18" s="122">
+      <c r="K18" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B18,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L18" s="122">
+      <c r="L18" s="123">
         <f>SUM(H18:K18)</f>
         <v/>
       </c>
-      <c r="M18" s="122">
+      <c r="M18" s="123">
         <f>G18+L18</f>
         <v/>
       </c>
-      <c r="N18" s="122">
+      <c r="N18" s="123">
         <f>SUM($M$11:M18)</f>
         <v/>
       </c>
@@ -5898,15 +6137,15 @@
         <f>B18</f>
         <v/>
       </c>
-      <c r="Q18" s="122">
+      <c r="Q18" s="123">
         <f>G18</f>
         <v/>
       </c>
-      <c r="R18" s="126">
+      <c r="R18" s="127">
         <f>-L18</f>
         <v/>
       </c>
-      <c r="S18" s="122">
+      <c r="S18" s="123">
         <f>N18</f>
         <v/>
       </c>
@@ -5921,47 +6160,47 @@
         <f>IF($B19=참고!$D$5,1,C20+1)</f>
         <v/>
       </c>
-      <c r="D19" s="122">
+      <c r="D19" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B19,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E19" s="122">
+      <c r="E19" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B19,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F19" s="122">
+      <c r="F19" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B19,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G19" s="122">
+      <c r="G19" s="123">
         <f>SUM(D19:F19)</f>
         <v/>
       </c>
-      <c r="H19" s="122">
+      <c r="H19" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B19,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I19" s="122">
+      <c r="I19" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B19,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J19" s="122">
+      <c r="J19" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B19,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K19" s="122">
+      <c r="K19" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B19,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L19" s="122">
+      <c r="L19" s="123">
         <f>SUM(H19:K19)</f>
         <v/>
       </c>
-      <c r="M19" s="122">
+      <c r="M19" s="123">
         <f>G19+L19</f>
         <v/>
       </c>
-      <c r="N19" s="122">
+      <c r="N19" s="123">
         <f>SUM($M$11:M19)</f>
         <v/>
       </c>
@@ -5969,15 +6208,15 @@
         <f>B19</f>
         <v/>
       </c>
-      <c r="Q19" s="122">
+      <c r="Q19" s="123">
         <f>G19</f>
         <v/>
       </c>
-      <c r="R19" s="126">
+      <c r="R19" s="127">
         <f>-L19</f>
         <v/>
       </c>
-      <c r="S19" s="122">
+      <c r="S19" s="123">
         <f>N19</f>
         <v/>
       </c>
@@ -5992,47 +6231,47 @@
         <f>IF($B20=참고!$D$5,1,C21+1)</f>
         <v/>
       </c>
-      <c r="D20" s="122">
+      <c r="D20" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B20,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E20" s="122">
+      <c r="E20" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B20,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F20" s="122">
+      <c r="F20" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B20,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G20" s="122">
+      <c r="G20" s="123">
         <f>SUM(D20:F20)</f>
         <v/>
       </c>
-      <c r="H20" s="122">
+      <c r="H20" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B20,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I20" s="122">
+      <c r="I20" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B20,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J20" s="122">
+      <c r="J20" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B20,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K20" s="122">
+      <c r="K20" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B20,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L20" s="122">
+      <c r="L20" s="123">
         <f>SUM(H20:K20)</f>
         <v/>
       </c>
-      <c r="M20" s="122">
+      <c r="M20" s="123">
         <f>G20+L20</f>
         <v/>
       </c>
-      <c r="N20" s="122">
+      <c r="N20" s="123">
         <f>SUM($M$11:M20)</f>
         <v/>
       </c>
@@ -6040,15 +6279,15 @@
         <f>B20</f>
         <v/>
       </c>
-      <c r="Q20" s="122">
+      <c r="Q20" s="123">
         <f>G20</f>
         <v/>
       </c>
-      <c r="R20" s="126">
+      <c r="R20" s="127">
         <f>-L20</f>
         <v/>
       </c>
-      <c r="S20" s="122">
+      <c r="S20" s="123">
         <f>N20</f>
         <v/>
       </c>
@@ -6063,47 +6302,47 @@
         <f>IF($B21=참고!$D$5,1,C22+1)</f>
         <v/>
       </c>
-      <c r="D21" s="122">
+      <c r="D21" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B21,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E21" s="122">
+      <c r="E21" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B21,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F21" s="122">
+      <c r="F21" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B21,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G21" s="122">
+      <c r="G21" s="123">
         <f>SUM(D21:F21)</f>
         <v/>
       </c>
-      <c r="H21" s="122">
+      <c r="H21" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B21,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I21" s="122">
+      <c r="I21" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B21,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J21" s="122">
+      <c r="J21" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B21,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K21" s="122">
+      <c r="K21" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B21,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L21" s="122">
+      <c r="L21" s="123">
         <f>SUM(H21:K21)</f>
         <v/>
       </c>
-      <c r="M21" s="122">
+      <c r="M21" s="123">
         <f>G21+L21</f>
         <v/>
       </c>
-      <c r="N21" s="122">
+      <c r="N21" s="123">
         <f>SUM($M$11:M21)</f>
         <v/>
       </c>
@@ -6111,15 +6350,15 @@
         <f>B21</f>
         <v/>
       </c>
-      <c r="Q21" s="122">
+      <c r="Q21" s="123">
         <f>G21</f>
         <v/>
       </c>
-      <c r="R21" s="126">
+      <c r="R21" s="127">
         <f>-L21</f>
         <v/>
       </c>
-      <c r="S21" s="122">
+      <c r="S21" s="123">
         <f>N21</f>
         <v/>
       </c>
@@ -6134,47 +6373,47 @@
         <f>IF($B22=참고!$D$5,1,C23+1)</f>
         <v/>
       </c>
-      <c r="D22" s="122">
+      <c r="D22" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B22,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E22" s="122">
+      <c r="E22" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B22,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F22" s="122">
+      <c r="F22" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B22,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G22" s="122">
+      <c r="G22" s="123">
         <f>SUM(D22:F22)</f>
         <v/>
       </c>
-      <c r="H22" s="122">
+      <c r="H22" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B22,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I22" s="122">
+      <c r="I22" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B22,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J22" s="122">
+      <c r="J22" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B22,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K22" s="122">
+      <c r="K22" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B22,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L22" s="122">
+      <c r="L22" s="123">
         <f>SUM(H22:K22)</f>
         <v/>
       </c>
-      <c r="M22" s="122">
+      <c r="M22" s="123">
         <f>G22+L22</f>
         <v/>
       </c>
-      <c r="N22" s="122">
+      <c r="N22" s="123">
         <f>SUM($M$11:M22)</f>
         <v/>
       </c>
@@ -6182,15 +6421,15 @@
         <f>B22</f>
         <v/>
       </c>
-      <c r="Q22" s="122">
+      <c r="Q22" s="123">
         <f>G22</f>
         <v/>
       </c>
-      <c r="R22" s="126">
+      <c r="R22" s="127">
         <f>-L22</f>
         <v/>
       </c>
-      <c r="S22" s="122">
+      <c r="S22" s="123">
         <f>N22</f>
         <v/>
       </c>
@@ -6205,47 +6444,47 @@
         <f>IF($B23=참고!$D$5,1,C24+1)</f>
         <v/>
       </c>
-      <c r="D23" s="122">
+      <c r="D23" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B23,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E23" s="122">
+      <c r="E23" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B23,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F23" s="122">
+      <c r="F23" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B23,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G23" s="122">
+      <c r="G23" s="123">
         <f>SUM(D23:F23)</f>
         <v/>
       </c>
-      <c r="H23" s="122">
+      <c r="H23" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B23,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I23" s="122">
+      <c r="I23" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B23,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J23" s="122">
+      <c r="J23" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B23,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K23" s="122">
+      <c r="K23" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B23,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L23" s="122">
+      <c r="L23" s="123">
         <f>SUM(H23:K23)</f>
         <v/>
       </c>
-      <c r="M23" s="122">
+      <c r="M23" s="123">
         <f>G23+L23</f>
         <v/>
       </c>
-      <c r="N23" s="122">
+      <c r="N23" s="123">
         <f>SUM($M$11:M23)</f>
         <v/>
       </c>
@@ -6253,15 +6492,15 @@
         <f>B23</f>
         <v/>
       </c>
-      <c r="Q23" s="122">
+      <c r="Q23" s="123">
         <f>G23</f>
         <v/>
       </c>
-      <c r="R23" s="126">
+      <c r="R23" s="127">
         <f>-L23</f>
         <v/>
       </c>
-      <c r="S23" s="122">
+      <c r="S23" s="123">
         <f>N23</f>
         <v/>
       </c>
@@ -6276,47 +6515,47 @@
         <f>IF($B24=참고!$D$5,1,C25+1)</f>
         <v/>
       </c>
-      <c r="D24" s="122">
+      <c r="D24" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B24,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E24" s="122">
+      <c r="E24" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B24,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F24" s="122">
+      <c r="F24" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B24,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G24" s="122">
+      <c r="G24" s="123">
         <f>SUM(D24:F24)</f>
         <v/>
       </c>
-      <c r="H24" s="122">
+      <c r="H24" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B24,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I24" s="122">
+      <c r="I24" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B24,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J24" s="122">
+      <c r="J24" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B24,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K24" s="122">
+      <c r="K24" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B24,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L24" s="122">
+      <c r="L24" s="123">
         <f>SUM(H24:K24)</f>
         <v/>
       </c>
-      <c r="M24" s="122">
+      <c r="M24" s="123">
         <f>G24+L24</f>
         <v/>
       </c>
-      <c r="N24" s="122">
+      <c r="N24" s="123">
         <f>SUM($M$11:M24)</f>
         <v/>
       </c>
@@ -6324,15 +6563,15 @@
         <f>B24</f>
         <v/>
       </c>
-      <c r="Q24" s="122">
+      <c r="Q24" s="123">
         <f>G24</f>
         <v/>
       </c>
-      <c r="R24" s="126">
+      <c r="R24" s="127">
         <f>-L24</f>
         <v/>
       </c>
-      <c r="S24" s="122">
+      <c r="S24" s="123">
         <f>N24</f>
         <v/>
       </c>
@@ -6347,47 +6586,47 @@
         <f>IF($B25=참고!$D$5,1,C26+1)</f>
         <v/>
       </c>
-      <c r="D25" s="122">
+      <c r="D25" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B25,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E25" s="122">
+      <c r="E25" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B25,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F25" s="122">
+      <c r="F25" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B25,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G25" s="122">
+      <c r="G25" s="123">
         <f>SUM(D25:F25)</f>
         <v/>
       </c>
-      <c r="H25" s="122">
+      <c r="H25" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B25,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I25" s="122">
+      <c r="I25" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B25,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J25" s="122">
+      <c r="J25" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B25,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K25" s="122">
+      <c r="K25" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B25,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L25" s="122">
+      <c r="L25" s="123">
         <f>SUM(H25:K25)</f>
         <v/>
       </c>
-      <c r="M25" s="122">
+      <c r="M25" s="123">
         <f>G25+L25</f>
         <v/>
       </c>
-      <c r="N25" s="122">
+      <c r="N25" s="123">
         <f>SUM($M$11:M25)</f>
         <v/>
       </c>
@@ -6395,15 +6634,15 @@
         <f>B25</f>
         <v/>
       </c>
-      <c r="Q25" s="122">
+      <c r="Q25" s="123">
         <f>G25</f>
         <v/>
       </c>
-      <c r="R25" s="126">
+      <c r="R25" s="127">
         <f>-L25</f>
         <v/>
       </c>
-      <c r="S25" s="122">
+      <c r="S25" s="123">
         <f>N25</f>
         <v/>
       </c>
@@ -6418,47 +6657,47 @@
         <f>IF($B26=참고!$D$5,1,C27+1)</f>
         <v/>
       </c>
-      <c r="D26" s="122">
+      <c r="D26" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B26,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E26" s="122">
+      <c r="E26" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B26,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F26" s="122">
+      <c r="F26" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B26,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G26" s="122">
+      <c r="G26" s="123">
         <f>SUM(D26:F26)</f>
         <v/>
       </c>
-      <c r="H26" s="122">
+      <c r="H26" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B26,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I26" s="122">
+      <c r="I26" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B26,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J26" s="122">
+      <c r="J26" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B26,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K26" s="122">
+      <c r="K26" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B26,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L26" s="122">
+      <c r="L26" s="123">
         <f>SUM(H26:K26)</f>
         <v/>
       </c>
-      <c r="M26" s="122">
+      <c r="M26" s="123">
         <f>G26+L26</f>
         <v/>
       </c>
-      <c r="N26" s="122">
+      <c r="N26" s="123">
         <f>SUM($M$11:M26)</f>
         <v/>
       </c>
@@ -6466,15 +6705,15 @@
         <f>B26</f>
         <v/>
       </c>
-      <c r="Q26" s="122">
+      <c r="Q26" s="123">
         <f>G26</f>
         <v/>
       </c>
-      <c r="R26" s="126">
+      <c r="R26" s="127">
         <f>-L26</f>
         <v/>
       </c>
-      <c r="S26" s="122">
+      <c r="S26" s="123">
         <f>N26</f>
         <v/>
       </c>
@@ -6489,47 +6728,47 @@
         <f>IF($B27=참고!$D$5,1,C28+1)</f>
         <v/>
       </c>
-      <c r="D27" s="122">
+      <c r="D27" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B27,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E27" s="122">
+      <c r="E27" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B27,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F27" s="122">
+      <c r="F27" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B27,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G27" s="122">
+      <c r="G27" s="123">
         <f>SUM(D27:F27)</f>
         <v/>
       </c>
-      <c r="H27" s="122">
+      <c r="H27" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B27,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I27" s="122">
+      <c r="I27" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B27,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J27" s="122">
+      <c r="J27" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B27,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K27" s="122">
+      <c r="K27" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B27,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L27" s="122">
+      <c r="L27" s="123">
         <f>SUM(H27:K27)</f>
         <v/>
       </c>
-      <c r="M27" s="122">
+      <c r="M27" s="123">
         <f>G27+L27</f>
         <v/>
       </c>
-      <c r="N27" s="122">
+      <c r="N27" s="123">
         <f>SUM($M$11:M27)</f>
         <v/>
       </c>
@@ -6537,15 +6776,15 @@
         <f>B27</f>
         <v/>
       </c>
-      <c r="Q27" s="122">
+      <c r="Q27" s="123">
         <f>G27</f>
         <v/>
       </c>
-      <c r="R27" s="126">
+      <c r="R27" s="127">
         <f>-L27</f>
         <v/>
       </c>
-      <c r="S27" s="122">
+      <c r="S27" s="123">
         <f>N27</f>
         <v/>
       </c>
@@ -6560,47 +6799,47 @@
         <f>IF($B28=참고!$D$5,1,C29+1)</f>
         <v/>
       </c>
-      <c r="D28" s="122">
+      <c r="D28" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B28,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E28" s="122">
+      <c r="E28" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B28,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F28" s="122">
+      <c r="F28" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B28,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G28" s="122">
+      <c r="G28" s="123">
         <f>SUM(D28:F28)</f>
         <v/>
       </c>
-      <c r="H28" s="122">
+      <c r="H28" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B28,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I28" s="122">
+      <c r="I28" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B28,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J28" s="122">
+      <c r="J28" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B28,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K28" s="122">
+      <c r="K28" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B28,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L28" s="122">
+      <c r="L28" s="123">
         <f>SUM(H28:K28)</f>
         <v/>
       </c>
-      <c r="M28" s="122">
+      <c r="M28" s="123">
         <f>G28+L28</f>
         <v/>
       </c>
-      <c r="N28" s="122">
+      <c r="N28" s="123">
         <f>SUM($M$11:M28)</f>
         <v/>
       </c>
@@ -6608,15 +6847,15 @@
         <f>B28</f>
         <v/>
       </c>
-      <c r="Q28" s="122">
+      <c r="Q28" s="123">
         <f>G28</f>
         <v/>
       </c>
-      <c r="R28" s="126">
+      <c r="R28" s="127">
         <f>-L28</f>
         <v/>
       </c>
-      <c r="S28" s="122">
+      <c r="S28" s="123">
         <f>N28</f>
         <v/>
       </c>
@@ -6631,47 +6870,47 @@
         <f>IF($B29=참고!$D$5,1,C30+1)</f>
         <v/>
       </c>
-      <c r="D29" s="122">
+      <c r="D29" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B29,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E29" s="122">
+      <c r="E29" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B29,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F29" s="122">
+      <c r="F29" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B29,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G29" s="122">
+      <c r="G29" s="123">
         <f>SUM(D29:F29)</f>
         <v/>
       </c>
-      <c r="H29" s="122">
+      <c r="H29" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B29,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I29" s="122">
+      <c r="I29" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B29,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J29" s="122">
+      <c r="J29" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B29,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K29" s="122">
+      <c r="K29" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B29,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L29" s="122">
+      <c r="L29" s="123">
         <f>SUM(H29:K29)</f>
         <v/>
       </c>
-      <c r="M29" s="122">
+      <c r="M29" s="123">
         <f>G29+L29</f>
         <v/>
       </c>
-      <c r="N29" s="122">
+      <c r="N29" s="123">
         <f>SUM($M$11:M29)</f>
         <v/>
       </c>
@@ -6679,15 +6918,15 @@
         <f>B29</f>
         <v/>
       </c>
-      <c r="Q29" s="122">
+      <c r="Q29" s="123">
         <f>G29</f>
         <v/>
       </c>
-      <c r="R29" s="126">
+      <c r="R29" s="127">
         <f>-L29</f>
         <v/>
       </c>
-      <c r="S29" s="122">
+      <c r="S29" s="123">
         <f>N29</f>
         <v/>
       </c>
@@ -6702,47 +6941,47 @@
         <f>IF($B30=참고!$D$5,1,C31+1)</f>
         <v/>
       </c>
-      <c r="D30" s="122">
+      <c r="D30" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B30,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E30" s="122">
+      <c r="E30" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B30,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F30" s="122">
+      <c r="F30" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B30,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G30" s="122">
+      <c r="G30" s="123">
         <f>SUM(D30:F30)</f>
         <v/>
       </c>
-      <c r="H30" s="122">
+      <c r="H30" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B30,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I30" s="122">
+      <c r="I30" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B30,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J30" s="122">
+      <c r="J30" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B30,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K30" s="122">
+      <c r="K30" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B30,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L30" s="122">
+      <c r="L30" s="123">
         <f>SUM(H30:K30)</f>
         <v/>
       </c>
-      <c r="M30" s="122">
+      <c r="M30" s="123">
         <f>G30+L30</f>
         <v/>
       </c>
-      <c r="N30" s="122">
+      <c r="N30" s="123">
         <f>SUM($M$11:M30)</f>
         <v/>
       </c>
@@ -6750,15 +6989,15 @@
         <f>B30</f>
         <v/>
       </c>
-      <c r="Q30" s="122">
+      <c r="Q30" s="123">
         <f>G30</f>
         <v/>
       </c>
-      <c r="R30" s="126">
+      <c r="R30" s="127">
         <f>-L30</f>
         <v/>
       </c>
-      <c r="S30" s="122">
+      <c r="S30" s="123">
         <f>N30</f>
         <v/>
       </c>
@@ -6773,47 +7012,47 @@
         <f>IF($B31=참고!$D$5,1,C32+1)</f>
         <v/>
       </c>
-      <c r="D31" s="122">
+      <c r="D31" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B31,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E31" s="122">
+      <c r="E31" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B31,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F31" s="122">
+      <c r="F31" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B31,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G31" s="122">
+      <c r="G31" s="123">
         <f>SUM(D31:F31)</f>
         <v/>
       </c>
-      <c r="H31" s="122">
+      <c r="H31" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B31,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I31" s="122">
+      <c r="I31" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B31,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J31" s="122">
+      <c r="J31" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B31,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K31" s="122">
+      <c r="K31" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B31,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L31" s="122">
+      <c r="L31" s="123">
         <f>SUM(H31:K31)</f>
         <v/>
       </c>
-      <c r="M31" s="122">
+      <c r="M31" s="123">
         <f>G31+L31</f>
         <v/>
       </c>
-      <c r="N31" s="122">
+      <c r="N31" s="123">
         <f>SUM($M$11:M31)</f>
         <v/>
       </c>
@@ -6821,15 +7060,15 @@
         <f>B31</f>
         <v/>
       </c>
-      <c r="Q31" s="122">
+      <c r="Q31" s="123">
         <f>G31</f>
         <v/>
       </c>
-      <c r="R31" s="126">
+      <c r="R31" s="127">
         <f>-L31</f>
         <v/>
       </c>
-      <c r="S31" s="122">
+      <c r="S31" s="123">
         <f>N31</f>
         <v/>
       </c>
@@ -6844,47 +7083,47 @@
         <f>IF($B32=참고!$D$5,1,C33+1)</f>
         <v/>
       </c>
-      <c r="D32" s="122">
+      <c r="D32" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B32,원장!$D:$D,증감분석!D$9,원장!$E:$E,증감분석!D$10)</f>
         <v/>
       </c>
-      <c r="E32" s="122">
+      <c r="E32" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B32,원장!$D:$D,증감분석!E$9,원장!$E:$E,증감분석!E$10)</f>
         <v/>
       </c>
-      <c r="F32" s="122">
+      <c r="F32" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B32,원장!$D:$D,증감분석!F$9,원장!$E:$E,증감분석!F$10)</f>
         <v/>
       </c>
-      <c r="G32" s="122">
+      <c r="G32" s="123">
         <f>SUM(D32:F32)</f>
         <v/>
       </c>
-      <c r="H32" s="122">
+      <c r="H32" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B32,원장!$D:$D,증감분석!H$9,원장!$E:$E,증감분석!H$10)</f>
         <v/>
       </c>
-      <c r="I32" s="122">
+      <c r="I32" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B32,원장!$D:$D,증감분석!I$9,원장!$E:$E,증감분석!I$10)</f>
         <v/>
       </c>
-      <c r="J32" s="122">
+      <c r="J32" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B32,원장!$D:$D,증감분석!J$9,원장!$E:$E,증감분석!J$10)</f>
         <v/>
       </c>
-      <c r="K32" s="122">
+      <c r="K32" s="123">
         <f>SUMIFS(원장!$H:$H,원장!$A:$A,증감분석!$B32,원장!$D:$D,증감분석!K$9,원장!$E:$E,증감분석!K$10)</f>
         <v/>
       </c>
-      <c r="L32" s="122">
+      <c r="L32" s="123">
         <f>SUM(H32:K32)</f>
         <v/>
       </c>
-      <c r="M32" s="122">
+      <c r="M32" s="123">
         <f>G32+L32</f>
         <v/>
       </c>
-      <c r="N32" s="122">
+      <c r="N32" s="123">
         <f>SUM($M$11:M32)</f>
         <v/>
       </c>
@@ -6892,15 +7131,15 @@
         <f>B32</f>
         <v/>
       </c>
-      <c r="Q32" s="122">
+      <c r="Q32" s="123">
         <f>G32</f>
         <v/>
       </c>
-      <c r="R32" s="126">
+      <c r="R32" s="127">
         <f>-L32</f>
         <v/>
       </c>
-      <c r="S32" s="122">
+      <c r="S32" s="123">
         <f>N32</f>
         <v/>
       </c>
@@ -7206,27 +7445,27 @@
           <t>입금액</t>
         </is>
       </c>
-      <c r="F10" s="127">
+      <c r="F10" s="128">
         <f>회비입출내역!$G$4</f>
         <v/>
       </c>
-      <c r="G10" s="128">
+      <c r="G10" s="129">
         <f>회비입출내역!$D$4</f>
         <v/>
       </c>
-      <c r="H10" s="129">
+      <c r="H10" s="130">
         <f>증감분석!$G$5</f>
         <v/>
       </c>
-      <c r="I10" s="129">
+      <c r="I10" s="130">
         <f>증감분석!$G$6</f>
         <v/>
       </c>
-      <c r="J10" s="129">
+      <c r="J10" s="130">
         <f>증감분석!$G$7</f>
         <v/>
       </c>
-      <c r="K10" s="130">
+      <c r="K10" s="131">
         <f>회비입출내역!$J$4</f>
         <v/>
       </c>
@@ -7239,27 +7478,27 @@
           <t>출금액</t>
         </is>
       </c>
-      <c r="F11" s="131">
+      <c r="F11" s="132">
         <f>회비입출내역!$G$9</f>
         <v/>
       </c>
-      <c r="G11" s="132">
+      <c r="G11" s="133">
         <f>회비입출내역!$D$9</f>
         <v/>
       </c>
-      <c r="H11" s="122">
+      <c r="H11" s="123">
         <f>증감분석!$L$5</f>
         <v/>
       </c>
-      <c r="I11" s="122">
+      <c r="I11" s="123">
         <f>증감분석!$L$6</f>
         <v/>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="123">
         <f>증감분석!$L$7</f>
         <v/>
       </c>
-      <c r="K11" s="133">
+      <c r="K11" s="134">
         <f>회비입출내역!$J$9</f>
         <v/>
       </c>
@@ -7272,27 +7511,27 @@
           <t>입금액 - 출금액</t>
         </is>
       </c>
-      <c r="F12" s="134">
+      <c r="F12" s="135">
         <f>SUM(F10:F11)</f>
         <v/>
       </c>
-      <c r="G12" s="126">
+      <c r="G12" s="127">
         <f>SUM(G10:G11)</f>
         <v/>
       </c>
-      <c r="H12" s="126">
+      <c r="H12" s="127">
         <f>SUM(H10:H11)</f>
         <v/>
       </c>
-      <c r="I12" s="126">
+      <c r="I12" s="127">
         <f>SUM(I10:I11)</f>
         <v/>
       </c>
-      <c r="J12" s="126">
+      <c r="J12" s="127">
         <f>SUM(J10:J11)</f>
         <v/>
       </c>
-      <c r="K12" s="122">
+      <c r="K12" s="123">
         <f>SUM(K10:K11)</f>
         <v/>
       </c>

--- a/finance/data/TO Score.xlsx
+++ b/finance/data/TO Score.xlsx
@@ -2204,7 +2204,9 @@
       <c r="E2" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F2" s="25" t="n"/>
+      <c r="F2" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G2" s="25" t="n"/>
       <c r="H2" s="25" t="n"/>
       <c r="I2" s="25" t="n"/>
@@ -2244,8 +2246,12 @@
       <c r="E3" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
+      <c r="F3" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G3" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H3" s="25" t="n"/>
       <c r="I3" s="25" t="n"/>
       <c r="J3" s="25" t="n"/>
@@ -2287,7 +2293,9 @@
       <c r="F4" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G4" s="25" t="n"/>
+      <c r="G4" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H4" s="25" t="n"/>
       <c r="I4" s="25" t="n"/>
       <c r="J4" s="25" t="n"/>
@@ -2326,8 +2334,12 @@
       <c r="E5" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
+      <c r="F5" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H5" s="25" t="n"/>
       <c r="I5" s="25" t="n"/>
       <c r="J5" s="25" t="n"/>
@@ -2369,7 +2381,9 @@
       <c r="F6" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G6" s="25" t="n"/>
+      <c r="G6" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H6" s="25" t="n"/>
       <c r="I6" s="25" t="n"/>
       <c r="J6" s="25" t="n"/>
@@ -2411,7 +2425,9 @@
       <c r="F7" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G7" s="25" t="n"/>
+      <c r="G7" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H7" s="25" t="n"/>
       <c r="I7" s="25" t="n"/>
       <c r="J7" s="25" t="n"/>
@@ -2453,7 +2469,9 @@
       <c r="F8" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G8" s="25" t="n"/>
+      <c r="G8" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H8" s="25" t="n"/>
       <c r="I8" s="25" t="n"/>
       <c r="J8" s="25" t="n"/>
@@ -2532,8 +2550,12 @@
       <c r="E10" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F10" s="25" t="n"/>
-      <c r="G10" s="25" t="n"/>
+      <c r="F10" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H10" s="25" t="n"/>
       <c r="I10" s="25" t="n"/>
       <c r="J10" s="25" t="n"/>
@@ -2575,7 +2597,9 @@
       <c r="F11" s="25" t="n">
         <v>40000</v>
       </c>
-      <c r="G11" s="25" t="n"/>
+      <c r="G11" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H11" s="25" t="n"/>
       <c r="I11" s="25" t="n"/>
       <c r="J11" s="25" t="n"/>
@@ -2614,8 +2638,12 @@
       <c r="E12" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="25" t="n"/>
+      <c r="F12" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G12" s="25" t="n">
+        <v>40000</v>
+      </c>
       <c r="H12" s="25" t="n"/>
       <c r="I12" s="25" t="n"/>
       <c r="J12" s="25" t="n"/>
@@ -2654,8 +2682,12 @@
       <c r="E13" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="25" t="n"/>
+      <c r="F13" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H13" s="25" t="n"/>
       <c r="I13" s="25" t="n"/>
       <c r="J13" s="25" t="n"/>
@@ -2694,7 +2726,9 @@
       <c r="E14" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F14" s="25" t="n"/>
+      <c r="F14" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G14" s="25" t="n"/>
       <c r="H14" s="25" t="n"/>
       <c r="I14" s="25" t="n"/>
@@ -2734,13 +2768,27 @@
       <c r="E15" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="25" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="25" t="n"/>
+      <c r="F15" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="M15" s="25" t="n"/>
       <c r="N15" s="25" t="n"/>
       <c r="O15" s="25" t="n"/>
@@ -2777,7 +2825,9 @@
       <c r="F16" s="25" t="n">
         <v>20000</v>
       </c>
-      <c r="G16" s="25" t="n"/>
+      <c r="G16" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="H16" s="25" t="n"/>
       <c r="I16" s="25" t="n"/>
       <c r="J16" s="25" t="n"/>
@@ -2900,7 +2950,9 @@
       <c r="E19" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F19" s="25" t="n"/>
+      <c r="F19" s="25" t="n">
+        <v>20000</v>
+      </c>
       <c r="G19" s="25" t="n"/>
       <c r="H19" s="25" t="n"/>
       <c r="I19" s="25" t="n"/>
@@ -3022,7 +3074,9 @@
       <c r="E22" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F22" s="103" t="n"/>
+      <c r="F22" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G22" s="103" t="n"/>
       <c r="H22" s="103" t="n"/>
       <c r="I22" s="103" t="n"/>
@@ -3065,7 +3119,9 @@
       <c r="F23" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G23" s="103" t="n"/>
+      <c r="G23" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H23" s="103" t="n"/>
       <c r="I23" s="103" t="n"/>
       <c r="J23" s="25" t="n"/>
@@ -3104,7 +3160,9 @@
       <c r="E24" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F24" s="103" t="n"/>
+      <c r="F24" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G24" s="103" t="n"/>
       <c r="H24" s="103" t="n"/>
       <c r="I24" s="103" t="n"/>
@@ -3147,7 +3205,9 @@
       <c r="F25" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G25" s="103" t="n"/>
+      <c r="G25" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H25" s="103" t="n"/>
       <c r="I25" s="103" t="n"/>
       <c r="J25" s="25" t="n"/>
@@ -3186,7 +3246,9 @@
       <c r="E26" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F26" s="103" t="n"/>
+      <c r="F26" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G26" s="103" t="n"/>
       <c r="H26" s="103" t="n"/>
       <c r="I26" s="103" t="n"/>
@@ -3311,7 +3373,9 @@
       <c r="F29" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G29" s="103" t="n"/>
+      <c r="G29" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H29" s="103" t="n"/>
       <c r="I29" s="103" t="n"/>
       <c r="J29" s="25" t="n"/>
@@ -3353,7 +3417,9 @@
       <c r="F30" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G30" s="103" t="n"/>
+      <c r="G30" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H30" s="103" t="n"/>
       <c r="I30" s="103" t="n"/>
       <c r="J30" s="25" t="n"/>
@@ -3392,7 +3458,9 @@
       <c r="E31" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F31" s="103" t="n"/>
+      <c r="F31" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G31" s="103" t="n"/>
       <c r="H31" s="103" t="n"/>
       <c r="I31" s="103" t="n"/>
@@ -3515,7 +3583,9 @@
       <c r="F34" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G34" s="103" t="n"/>
+      <c r="G34" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H34" s="103" t="n"/>
       <c r="I34" s="103" t="n"/>
       <c r="J34" s="25" t="n"/>
@@ -3594,7 +3664,9 @@
       <c r="E36" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F36" s="103" t="n"/>
+      <c r="F36" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G36" s="103" t="n"/>
       <c r="H36" s="103" t="n"/>
       <c r="I36" s="103" t="n"/>
@@ -3637,7 +3709,9 @@
       <c r="F37" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G37" s="103" t="n"/>
+      <c r="G37" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H37" s="103" t="n"/>
       <c r="I37" s="103" t="n"/>
       <c r="J37" s="25" t="n"/>
@@ -3675,12 +3749,24 @@
       <c r="E38" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F38" s="103" t="n"/>
-      <c r="G38" s="103" t="n"/>
-      <c r="H38" s="103" t="n"/>
-      <c r="I38" s="103" t="n"/>
-      <c r="J38" s="103" t="n"/>
-      <c r="K38" s="103" t="n"/>
+      <c r="F38" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G38" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H38" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="I38" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J38" s="103" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K38" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="L38" s="103" t="n"/>
       <c r="M38" s="103" t="n"/>
       <c r="N38" s="103" t="n"/>
@@ -3718,7 +3804,9 @@
       <c r="F39" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G39" s="103" t="n"/>
+      <c r="G39" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H39" s="103" t="n"/>
       <c r="I39" s="103" t="n"/>
       <c r="J39" s="103" t="n"/>
@@ -3760,7 +3848,9 @@
       <c r="F40" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G40" s="103" t="n"/>
+      <c r="G40" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H40" s="103" t="n"/>
       <c r="I40" s="103" t="n"/>
       <c r="J40" s="25" t="n"/>
@@ -3799,7 +3889,9 @@
       <c r="E41" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="F41" s="103" t="n"/>
+      <c r="F41" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="G41" s="103" t="n"/>
       <c r="H41" s="103" t="n"/>
       <c r="I41" s="103" t="n"/>
@@ -3842,7 +3934,9 @@
       <c r="F42" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G42" s="103" t="n"/>
+      <c r="G42" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H42" s="103" t="n"/>
       <c r="I42" s="103" t="n"/>
       <c r="J42" s="25" t="n"/>
@@ -3882,7 +3976,9 @@
       <c r="F43" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G43" s="103" t="n"/>
+      <c r="G43" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H43" s="103" t="n"/>
       <c r="I43" s="103" t="n"/>
       <c r="J43" s="25" t="n"/>
@@ -3920,7 +4016,9 @@
       <c r="F44" s="103" t="n">
         <v>20000</v>
       </c>
-      <c r="G44" s="103" t="n"/>
+      <c r="G44" s="103" t="n">
+        <v>20000</v>
+      </c>
       <c r="H44" s="103" t="n"/>
       <c r="I44" s="103" t="n"/>
       <c r="J44" s="25" t="n"/>
@@ -4484,7 +4582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="13.25" customWidth="1" style="97" min="1" max="1"/>
@@ -5133,6 +5231,115 @@
         <v/>
       </c>
       <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>월간회비납부</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4">
+        <f>RIGHT(YEAR(C18),2)&amp;"년 "&amp;MONTH(C18)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B18" s="4">
+        <f>VLOOKUP(WEEKDAY(C18,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C18" s="136" t="n">
+        <v>46222</v>
+      </c>
+      <c r="D18" s="136" t="inlineStr">
+        <is>
+          <t>출금</t>
+        </is>
+      </c>
+      <c r="E18" s="136" t="inlineStr">
+        <is>
+          <t>모임비</t>
+        </is>
+      </c>
+      <c r="F18" s="137" t="n">
+        <v>559000</v>
+      </c>
+      <c r="G18" s="137" t="n"/>
+      <c r="H18" s="138">
+        <f>G18-F18</f>
+        <v/>
+      </c>
+      <c r="I18" s="139" t="inlineStr">
+        <is>
+          <t>카카오페이 자동이체, 7월 모임비</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4">
+        <f>RIGHT(YEAR(C19),2)&amp;"년 "&amp;MONTH(C19)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B19" s="4">
+        <f>VLOOKUP(WEEKDAY(C19,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C19" s="136" t="n">
+        <v>46228</v>
+      </c>
+      <c r="D19" s="136" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="E19" s="136" t="inlineStr">
+        <is>
+          <t>이자</t>
+        </is>
+      </c>
+      <c r="F19" s="137" t="n"/>
+      <c r="G19" s="137" t="n">
+        <v>81</v>
+      </c>
+      <c r="H19" s="138">
+        <f>G19-F19</f>
+        <v/>
+      </c>
+      <c r="I19" s="139" t="inlineStr">
+        <is>
+          <t>월간이자</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4">
+        <f>RIGHT(YEAR(C20),2)&amp;"년 "&amp;MONTH(C20)&amp;"월"</f>
+        <v/>
+      </c>
+      <c r="B20" s="4">
+        <f>VLOOKUP(WEEKDAY(C20,2),참조!$A$1:$B$10,2,)</f>
+        <v/>
+      </c>
+      <c r="C20" s="136" t="n">
+        <v>46388</v>
+      </c>
+      <c r="D20" s="136" t="inlineStr">
+        <is>
+          <t>입금</t>
+        </is>
+      </c>
+      <c r="E20" s="136" t="inlineStr">
+        <is>
+          <t>회비</t>
+        </is>
+      </c>
+      <c r="F20" s="137" t="n"/>
+      <c r="G20" s="137">
+        <f>SUMIFS(입금현황!$45:$45,입금현황!$1:$1,원장!$A20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="138">
+        <f>G20-F20</f>
+        <v/>
+      </c>
+      <c r="I20" s="139" t="inlineStr">
         <is>
           <t>월간회비납부</t>
         </is>

--- a/finance/data/TO Score.xlsx
+++ b/finance/data/TO Score.xlsx
@@ -4505,11 +4505,11 @@
       <c r="H16" s="17" t="n"/>
       <c r="I16" s="117" t="inlineStr">
         <is>
-          <t>7월 1일 잔액</t>
+          <t>8월 3일 잔액</t>
         </is>
       </c>
       <c r="J16" s="118" t="n">
-        <v>957190</v>
+        <v>1398271</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1" s="97">

--- a/finance/data/TO Score.xlsx
+++ b/finance/data/TO Score.xlsx
@@ -2497,7 +2497,7 @@
       </c>
       <c r="B9" s="101" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>탈퇴</t>
         </is>
       </c>
       <c r="C9" s="102">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="B21" s="101" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>탈퇴</t>
         </is>
       </c>
       <c r="C21" s="102">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B28" s="101" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>탈퇴</t>
         </is>
       </c>
       <c r="C28" s="102">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B35" s="101" t="inlineStr">
         <is>
-          <t>유지</t>
+          <t>탈퇴</t>
         </is>
       </c>
       <c r="C35" s="102">

--- a/finance/data/TO Score.xlsx
+++ b/finance/data/TO Score.xlsx
@@ -2750,7 +2750,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>김성환</t>
+          <t>김성환(82)</t>
         </is>
       </c>
       <c r="B15" s="101" t="inlineStr">
